--- a/ZonasEscolares/excels/LIMA-LIMA-EL_AGUSTINO.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-EL_AGUSTINO.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>EL_AGUSTINO</t>
+          <t>EL AGUSTINO</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-EL_AGUSTINO.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-EL_AGUSTINO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>08 VILLA HERMOSA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.0408</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-76.98958</v>
-      </c>
-      <c r="I2" t="n">
-        <v>217</v>
-      </c>
-      <c r="J2" t="n">
-        <v>11</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.0408</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-76.98958</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>0009 JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.02803</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-76.98938</v>
-      </c>
-      <c r="I3" t="n">
-        <v>727</v>
-      </c>
-      <c r="J3" t="n">
-        <v>31</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.02803</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-76.98938</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>013 SANTA ROSITA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.03934</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-76.99666999999999</v>
-      </c>
-      <c r="I4" t="n">
-        <v>291</v>
-      </c>
-      <c r="J4" t="n">
-        <v>11</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.03934</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-76.99667</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>017 CUNA JARDIN</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.0514</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-76.99939000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>565</v>
-      </c>
-      <c r="J5" t="n">
-        <v>23</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.0514</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-76.99939</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>046 LOS LIBERTADORES DE AYACUCHO</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.05624</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-76.99453</v>
-      </c>
-      <c r="I6" t="n">
-        <v>877</v>
-      </c>
-      <c r="J6" t="n">
-        <v>43</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.05624</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-76.99453</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>877</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>048 SAN JUAN BOSCO</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.060027</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-77.002724</v>
-      </c>
-      <c r="I7" t="n">
-        <v>270</v>
-      </c>
-      <c r="J7" t="n">
-        <v>14</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.060027</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-77.002724</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>0049 ANTONIA MORENO DE CACERES</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.0521</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-77.00190000000001</v>
-      </c>
-      <c r="I8" t="n">
-        <v>709</v>
-      </c>
-      <c r="J8" t="n">
-        <v>30</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.0521</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-77.0019</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>068</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.02776</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-76.99299000000001</v>
-      </c>
-      <c r="I9" t="n">
-        <v>272</v>
-      </c>
-      <c r="J9" t="n">
-        <v>14</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.02776</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-76.99299</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>069 NOCHETO LUIS ENRIQUE VI</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-12.04508</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-76.98547000000001</v>
-      </c>
-      <c r="I10" t="n">
-        <v>207</v>
-      </c>
-      <c r="J10" t="n">
-        <v>11</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.04508</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-76.98547</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>076 MICAELA BASTIDAS</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-12.05093</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-76.99544</v>
-      </c>
-      <c r="I11" t="n">
-        <v>147</v>
-      </c>
-      <c r="J11" t="n">
-        <v>9</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-12.05093</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-76.99544</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>081</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-12.03737</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-77.00588999999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>207</v>
-      </c>
-      <c r="J12" t="n">
-        <v>9</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-12.03737</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-77.00589</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>0085 JOSE DE LA TORRE UGARTE</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.0379</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-76.99063</v>
-      </c>
-      <c r="I13" t="n">
-        <v>839</v>
-      </c>
-      <c r="J13" t="n">
-        <v>38</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.0379</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-76.99063</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>0093 FERNANDO BELAUNDE TERRY</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-12.03924</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-76.99657999999999</v>
-      </c>
-      <c r="I14" t="n">
-        <v>441</v>
-      </c>
-      <c r="J14" t="n">
-        <v>18</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-12.03924</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-76.99658</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>112 HEROES DE LA BREÑA</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.03062</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-76.99718</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1344</v>
-      </c>
-      <c r="J15" t="n">
-        <v>59</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.03062</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-76.99718</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1344</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>115 TORIBIO RODRIGUEZ DE MENDOZA</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.0343</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-77.006</v>
-      </c>
-      <c r="I16" t="n">
-        <v>854</v>
-      </c>
-      <c r="J16" t="n">
-        <v>41</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.0343</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-77.006</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>854</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>127 SAN JOSE</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-12.03325</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-77.00305</v>
-      </c>
-      <c r="I17" t="n">
-        <v>782</v>
-      </c>
-      <c r="J17" t="n">
-        <v>32</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-12.03325</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-77.00305</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>782</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>134 RAMIRO PRIALE</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-12.031899</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-77.008878</v>
-      </c>
-      <c r="I18" t="n">
-        <v>697</v>
-      </c>
-      <c r="J18" t="n">
-        <v>33</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-12.031899</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-77.008878</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>1025 MARIA PARADO DE BELLIDO</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-12.050187</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-77.006187</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1003</v>
-      </c>
-      <c r="J19" t="n">
-        <v>46</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-12.050187</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-77.006187</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>1044 MARIA REICHE NEWMANN</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-12.044016</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-77.003</v>
-      </c>
-      <c r="I20" t="n">
-        <v>887</v>
-      </c>
-      <c r="J20" t="n">
-        <v>34</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-12.044016</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-77.003</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>1045 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-12.0422</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-76.9894</v>
-      </c>
-      <c r="I21" t="n">
-        <v>541</v>
-      </c>
-      <c r="J21" t="n">
-        <v>24</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-12.0422</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-76.9894</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>1046 JULIO RAMON RIBEYRO</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-12.05059</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-77.00892</v>
-      </c>
-      <c r="I22" t="n">
-        <v>205</v>
-      </c>
-      <c r="J22" t="n">
-        <v>10</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-12.05059</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-77.00892</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>1047 JUANA INFANTES VERA</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-12.03318</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-76.98887999999999</v>
-      </c>
-      <c r="I23" t="n">
-        <v>845</v>
-      </c>
-      <c r="J23" t="n">
-        <v>38</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-12.03318</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-76.98888</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>1169 ALMIRANTE MIGUEL GRAU S / 1169 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-12.05152</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-77.00442</v>
-      </c>
-      <c r="I24" t="n">
-        <v>473</v>
-      </c>
-      <c r="J24" t="n">
-        <v>23</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-12.05152</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-77.00442</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>1171 JORGE BASADRE GROHMANN</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-12.055789</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-77.00160200000001</v>
-      </c>
-      <c r="I25" t="n">
-        <v>802</v>
-      </c>
-      <c r="J25" t="n">
-        <v>36</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-12.055789</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-77.001602</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>GLORIOSOS HUSARES DE JUNIN</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-12.0515</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-76.9987</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1608</v>
-      </c>
-      <c r="J26" t="n">
-        <v>75</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-12.0515</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-76.9987</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1608</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>1177 HEROES DEL CENEPA</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-12.05896</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-77.00256</v>
-      </c>
-      <c r="I27" t="n">
-        <v>315</v>
-      </c>
-      <c r="J27" t="n">
-        <v>13</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-12.05896</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-77.00256</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>1186 SANTA ROSA DE LIMA MILAGROSA</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-12.0596</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-76.99679</v>
-      </c>
-      <c r="I28" t="n">
-        <v>442</v>
-      </c>
-      <c r="J28" t="n">
-        <v>22</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-12.0596</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-76.99679</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>1187 SAN CAYETANO</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-12.05678</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-77.00766</v>
-      </c>
-      <c r="I29" t="n">
-        <v>364</v>
-      </c>
-      <c r="J29" t="n">
-        <v>17</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-12.05678</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-77.00766</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>HOGAR SAN MARTIN</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-12.0542</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-77.0069</v>
-      </c>
-      <c r="I30" t="n">
-        <v>217</v>
-      </c>
-      <c r="J30" t="n">
-        <v>11</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-12.0542</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-77.0069</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>LA PRADERA II</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-12.0303</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-76.96305</v>
-      </c>
-      <c r="I31" t="n">
-        <v>573</v>
-      </c>
-      <c r="J31" t="n">
-        <v>21</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-12.0303</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-76.96305</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>NICOLAS DE PIEROLA</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-12.05079</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-77.0107</v>
-      </c>
-      <c r="I32" t="n">
-        <v>396</v>
-      </c>
-      <c r="J32" t="n">
-        <v>19</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-12.05079</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-77.0107</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>AUGUSTO N. WISSE</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-12.03869</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-76.99016</v>
-      </c>
-      <c r="I33" t="n">
-        <v>206</v>
-      </c>
-      <c r="J33" t="n">
-        <v>11</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-12.03869</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-76.99016</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>ALELUYA</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-12.0504</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-76.99744</v>
-      </c>
-      <c r="I34" t="n">
-        <v>178</v>
-      </c>
-      <c r="J34" t="n">
-        <v>14</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-12.0504</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-76.99744</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>FE Y ALEGRIA 39</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-12.0433</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-76.98990000000001</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1465</v>
-      </c>
-      <c r="J35" t="n">
-        <v>62</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-12.0433</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-76.9899</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1465</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>DORA MAYER</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-12.05226</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-77.00583</v>
-      </c>
-      <c r="I36" t="n">
-        <v>116</v>
-      </c>
-      <c r="J36" t="n">
-        <v>14</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-12.05226</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-77.00583</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>IGNACIO MERINO</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-12.05523</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-77.00642000000001</v>
-      </c>
-      <c r="I37" t="n">
-        <v>251</v>
-      </c>
-      <c r="J37" t="n">
-        <v>17</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-12.05523</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-77.00642</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>JOHANNES GUTENBERG</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-12.04798</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-76.99687</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1320</v>
-      </c>
-      <c r="J38" t="n">
-        <v>72</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-12.04798</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-76.99687</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>ALEXANDER FLEMING</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-12.0321</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-76.9997</v>
-      </c>
-      <c r="I39" t="n">
-        <v>240</v>
-      </c>
-      <c r="J39" t="n">
-        <v>14</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-12.0321</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-76.9997</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-12.0306</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-76.99845999999999</v>
-      </c>
-      <c r="I40" t="n">
-        <v>34</v>
-      </c>
-      <c r="J40" t="n">
-        <v>3</v>
-      </c>
-      <c r="K40" t="n">
-        <v>1</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-12.0306</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-76.99846</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>ESTRELLITA DE JESUS</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-12.04336</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-76.986953</v>
-      </c>
-      <c r="I41" t="n">
-        <v>57</v>
-      </c>
-      <c r="J41" t="n">
-        <v>6</v>
-      </c>
-      <c r="K41" t="n">
-        <v>1</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-12.04336</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-76.986953</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>PASCUAL SACO OLIVEROS</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-12.03405</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-76.99737</v>
-      </c>
-      <c r="I42" t="n">
-        <v>851</v>
-      </c>
-      <c r="J42" t="n">
-        <v>27</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-12.03405</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-76.99737</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>VIRGEN MARIA</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-12.04911</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-77.00014</v>
-      </c>
-      <c r="I43" t="n">
-        <v>329</v>
-      </c>
-      <c r="J43" t="n">
-        <v>26</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-12.04911</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-77.00014</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>SANTA RITA</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-12.03323</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-76.99778999999999</v>
-      </c>
-      <c r="I44" t="n">
-        <v>803</v>
-      </c>
-      <c r="J44" t="n">
-        <v>27</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-12.03323</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-76.99779</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>803</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>DIVINO NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-12.0306</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-76.9987</v>
-      </c>
-      <c r="I45" t="n">
-        <v>104</v>
-      </c>
-      <c r="J45" t="n">
-        <v>5</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-12.0306</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-76.9987</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>CRISTO REDENTOR</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-12.05627</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-77.00747</v>
-      </c>
-      <c r="I46" t="n">
-        <v>421</v>
-      </c>
-      <c r="J46" t="n">
-        <v>15</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-12.05627</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-77.00747</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>ANTONIO ELEUTER</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-12.05646</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-77.00601</v>
-      </c>
-      <c r="I47" t="n">
-        <v>240</v>
-      </c>
-      <c r="J47" t="n">
-        <v>17</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-12.05646</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-77.00601</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>CUNA JARDIN PARROQUIAL SAN JOSE</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-12.05879</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-76.99526</v>
-      </c>
-      <c r="I48" t="n">
-        <v>143</v>
-      </c>
-      <c r="J48" t="n">
-        <v>6</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-12.05879</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-76.99526</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>NICOLA DE BARI</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-12.03104</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-76.99451000000001</v>
-      </c>
-      <c r="I49" t="n">
-        <v>16</v>
-      </c>
-      <c r="J49" t="n">
-        <v>2</v>
-      </c>
-      <c r="K49" t="n">
-        <v>1</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-12.03104</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-76.99451</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>SAN CARLOS DE LA CORPORACION</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-12.05011</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-76.99930999999999</v>
-      </c>
-      <c r="I50" t="n">
-        <v>305</v>
-      </c>
-      <c r="J50" t="n">
-        <v>15</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-12.05011</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-76.99931</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>SAN MIGUEL EMPRENDEDOR</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-12.04564</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-76.99930999999999</v>
-      </c>
-      <c r="I51" t="n">
-        <v>233</v>
-      </c>
-      <c r="J51" t="n">
-        <v>25</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-12.04564</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-76.99931</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>LA PRADERA II</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-12.03034</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-76.96305</v>
-      </c>
-      <c r="I52" t="n">
-        <v>362</v>
-      </c>
-      <c r="J52" t="n">
-        <v>18</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-12.03034</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-76.96305</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>JUVENTUD CIENTIFICA</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-12.043875</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-76.99955199999999</v>
-      </c>
-      <c r="I53" t="n">
-        <v>183</v>
-      </c>
-      <c r="J53" t="n">
-        <v>13</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-12.043875</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-76.999552</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>LA PIZARRA DE JUGUETE</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-12.03472</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-76.99981</v>
-      </c>
-      <c r="I54" t="n">
-        <v>94</v>
-      </c>
-      <c r="J54" t="n">
-        <v>5</v>
-      </c>
-      <c r="K54" t="n">
-        <v>1</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-12.03472</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-76.99981</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LIMA-LIMA-EL_AGUSTINO.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-EL_AGUSTINO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>304704</t>
+          <t>304978</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>08 VILLA HERMOSA</t>
+          <t>1046 JULIO RAMON RIBEYRO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.0408</t>
+          <t>-12.05059</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.98958</t>
+          <t>-77.00892</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>205</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>304718</t>
+          <t>304704</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0009 JOSE MARIA ARGUEDAS</t>
+          <t>08 VILLA HERMOSA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.02803</t>
+          <t>-12.0408</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.98938</t>
+          <t>-76.98958</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>217</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>304756</t>
+          <t>304822</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>017 CUNA JARDIN</t>
+          <t>069 NOCHETO LUIS ENRIQUE VI</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.0514</t>
+          <t>-12.04508</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.99939</t>
+          <t>-76.98547</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>207</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>304761</t>
+          <t>305100</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>046 LOS LIBERTADORES DE AYACUCHO</t>
+          <t>HOGAR SAN MARTIN</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.05624</t>
+          <t>-12.0542</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.99453</t>
+          <t>-77.0069</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>217</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>304780</t>
+          <t>305143</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>048 SAN JUAN BOSCO</t>
+          <t>AUGUSTO N. WISSE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.060027</t>
+          <t>-12.03869</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.002724</t>
+          <t>-76.99016</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>206</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>304799</t>
+          <t>305044</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0049 ANTONIA MORENO DE CACERES</t>
+          <t>1177 HEROES DEL CENEPA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.0521</t>
+          <t>-12.05896</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.0019</t>
+          <t>-77.00256</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>315</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>304817</t>
+          <t>908252</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>068</t>
+          <t>JUVENTUD CIENTIFICA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.02776</t>
+          <t>-12.043875</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.99299</t>
+          <t>-76.999552</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>183</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>304822</t>
+          <t>304780</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>069 NOCHETO LUIS ENRIQUE VI</t>
+          <t>048 SAN JUAN BOSCO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.04508</t>
+          <t>-12.060027</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.98547</t>
+          <t>-77.002724</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>270</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>304836</t>
+          <t>304817</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>076 MICAELA BASTIDAS</t>
+          <t>068</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.05093</t>
+          <t>-12.02776</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.99544</t>
+          <t>-76.99299</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>272</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>304841</t>
+          <t>305157</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>081</t>
+          <t>ALELUYA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.03737</t>
+          <t>-12.0504</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.00589</t>
+          <t>-76.99744</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>178</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1183,42 +1183,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>304860</t>
+          <t>305218</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0085 JOSE DE LA TORRE UGARTE</t>
+          <t>DORA MAYER</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.0379</t>
+          <t>-12.05226</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.99063</t>
+          <t>-77.00583</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>116</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>304879</t>
+          <t>305299</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0093 FERNANDO BELAUNDE TERRY</t>
+          <t>ALEXANDER FLEMING</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.03924</t>
+          <t>-12.0321</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.99658</t>
+          <t>-76.9997</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>240</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>304898</t>
+          <t>588340</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>112 HEROES DE LA BREÑA</t>
+          <t>CRISTO REDENTOR</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.03062</t>
+          <t>-12.05627</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.99718</t>
+          <t>-77.00747</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>421</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>304916</t>
+          <t>834930</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>115 TORIBIO RODRIGUEZ DE MENDOZA</t>
+          <t>SAN CARLOS DE LA CORPORACION</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.0343</t>
+          <t>-12.05011</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.006</t>
+          <t>-76.99931</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>305</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>304921</t>
+          <t>305077</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>127 SAN JOSE</t>
+          <t>1187 SAN CAYETANO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.03325</t>
+          <t>-12.05678</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.00305</t>
+          <t>-77.00766</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>364</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>304935</t>
+          <t>305256</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>134 RAMIRO PRIALE</t>
+          <t>IGNACIO MERINO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.031899</t>
+          <t>-12.05523</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.008878</t>
+          <t>-77.00642</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>251</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>304940</t>
+          <t>602001</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1025 MARIA PARADO DE BELLIDO</t>
+          <t>ANTONIO ELEUTER</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.050187</t>
+          <t>-12.05646</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.006187</t>
+          <t>-77.00601</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>240</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>304959</t>
+          <t>304879</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1044 MARIA REICHE NEWMANN</t>
+          <t>0093 FERNANDO BELAUNDE TERRY</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.044016</t>
+          <t>-12.03924</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.003</t>
+          <t>-76.99658</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>441</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>304964</t>
+          <t>858756</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1045 NUESTRA SEÑORA DE FATIMA</t>
+          <t>LA PRADERA II</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.0422</t>
+          <t>-12.03034</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.9894</t>
+          <t>-76.96305</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>362</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>304978</t>
+          <t>305124</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1046 JULIO RAMON RIBEYRO</t>
+          <t>NICOLAS DE PIEROLA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.05059</t>
+          <t>-12.05079</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.00892</t>
+          <t>-77.0107</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>396</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,37 +1803,37 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>304983</t>
+          <t>786806</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1047 JUANA INFANTES VERA</t>
+          <t>NICOLA DE BARI</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.03318</t>
+          <t>-12.03104</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.98888</t>
+          <t>-76.99451</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>305001</t>
+          <t>305119</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1169 ALMIRANTE MIGUEL GRAU S / 1169 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
+          <t>LA PRADERA II</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.05152</t>
+          <t>-12.0303</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.00442</t>
+          <t>-76.96305</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>573</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>305020</t>
+          <t>305063</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1171 JORGE BASADRE GROHMANN</t>
+          <t>1186 SANTA ROSA DE LIMA MILAGROSA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.055789</t>
+          <t>-12.0596</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.001602</t>
+          <t>-76.99679</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>442</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>305039</t>
+          <t>304756</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>GLORIOSOS HUSARES DE JUNIN</t>
+          <t>017 CUNA JARDIN</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.0515</t>
+          <t>-12.0514</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.9987</t>
+          <t>-76.99939</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>565</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>305044</t>
+          <t>305001</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1177 HEROES DEL CENEPA</t>
+          <t>1169 ALMIRANTE MIGUEL GRAU S / 1169 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.05896</t>
+          <t>-12.05152</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.00256</t>
+          <t>-77.00442</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>473</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>305063</t>
+          <t>304964</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1186 SANTA ROSA DE LIMA MILAGROSA</t>
+          <t>1045 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.0596</t>
+          <t>-12.0422</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.99679</t>
+          <t>-76.9894</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>541</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>305077</t>
+          <t>846301</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1187 SAN CAYETANO</t>
+          <t>SAN MIGUEL EMPRENDEDOR</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.05678</t>
+          <t>-12.04564</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.00766</t>
+          <t>-76.99931</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>233</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>305100</t>
+          <t>544068</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>HOGAR SAN MARTIN</t>
+          <t>VIRGEN MARIA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.0542</t>
+          <t>-12.04911</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.0069</t>
+          <t>-77.00014</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>329</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>305119</t>
+          <t>490503</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>LA PRADERA II</t>
+          <t>PASCUAL SACO OLIVEROS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.0303</t>
+          <t>-12.03405</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.96305</t>
+          <t>-76.99737</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>851</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>305124</t>
+          <t>564259</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NICOLAS DE PIEROLA</t>
+          <t>SANTA RITA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.05079</t>
+          <t>-12.03323</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-77.0107</t>
+          <t>-76.99779</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>803</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,37 +2423,37 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>305143</t>
+          <t>305360</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AUGUSTO N. WISSE</t>
+          <t>NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.03869</t>
+          <t>-12.0306</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-76.99016</t>
+          <t>-76.99846</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>305157</t>
+          <t>304799</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ALELUYA</t>
+          <t>0049 ANTONIA MORENO DE CACERES</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.0504</t>
+          <t>-12.0521</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-76.99744</t>
+          <t>-77.0019</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>709</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>305162</t>
+          <t>304718</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 39</t>
+          <t>0009 JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.0433</t>
+          <t>-12.02803</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-76.9899</t>
+          <t>-76.98938</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>727</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,37 +2609,37 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>305218</t>
+          <t>304921</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>DORA MAYER</t>
+          <t>127 SAN JOSE</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.05226</t>
+          <t>-12.03325</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-77.00583</t>
+          <t>-77.00305</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>782</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>305256</t>
+          <t>304935</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>IGNACIO MERINO</t>
+          <t>134 RAMIRO PRIALE</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.05523</t>
+          <t>-12.031899</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-77.00642</t>
+          <t>-77.008878</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>697</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>305261</t>
+          <t>304959</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>JOHANNES GUTENBERG</t>
+          <t>1044 MARIA REICHE NEWMANN</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.04798</t>
+          <t>-12.044016</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.99687</t>
+          <t>-77.003</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>887</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>305299</t>
+          <t>305020</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ALEXANDER FLEMING</t>
+          <t>1171 JORGE BASADRE GROHMANN</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.0321</t>
+          <t>-12.055789</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-76.9997</t>
+          <t>-77.001602</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>802</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,42 +2857,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>305360</t>
+          <t>304860</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL CARMEN</t>
+          <t>0085 JOSE DE LA TORRE UGARTE</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.0306</t>
+          <t>-12.0379</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-76.99846</t>
+          <t>-76.99063</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>839</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2919,42 +2919,42 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>328248</t>
+          <t>304983</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ESTRELLITA DE JESUS</t>
+          <t>1047 JUANA INFANTES VERA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.04336</t>
+          <t>-12.03318</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-76.986953</t>
+          <t>-76.98888</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>845</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>490503</t>
+          <t>304916</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PASCUAL SACO OLIVEROS</t>
+          <t>115 TORIBIO RODRIGUEZ DE MENDOZA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.03405</t>
+          <t>-12.0343</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-76.99737</t>
+          <t>-77.006</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>854</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>544068</t>
+          <t>304761</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>VIRGEN MARIA</t>
+          <t>046 LOS LIBERTADORES DE AYACUCHO</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.04911</t>
+          <t>-12.05624</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-77.00014</t>
+          <t>-76.99453</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>877</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>564259</t>
+          <t>304940</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SANTA RITA</t>
+          <t>1025 MARIA PARADO DE BELLIDO</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.03323</t>
+          <t>-12.050187</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-76.99779</t>
+          <t>-77.006187</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3229,37 +3229,37 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>588340</t>
+          <t>999290</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CRISTO REDENTOR</t>
+          <t>LA PIZARRA DE JUGUETE</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.05627</t>
+          <t>-12.03472</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-77.00747</t>
+          <t>-76.99981</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>602001</t>
+          <t>304898</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ANTONIO ELEUTER</t>
+          <t>112 HEROES DE LA BREÑA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-12.05646</t>
+          <t>-12.03062</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-77.00601</t>
+          <t>-76.99718</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,27 +3353,27 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>714225</t>
+          <t>328248</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CUNA JARDIN PARROQUIAL SAN JOSE</t>
+          <t>ESTRELLITA DE JESUS</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-12.05879</t>
+          <t>-12.04336</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-76.99526</t>
+          <t>-76.986953</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3415,42 +3415,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>786806</t>
+          <t>714225</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>NICOLA DE BARI</t>
+          <t>CUNA JARDIN PARROQUIAL SAN JOSE</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.03104</t>
+          <t>-12.05879</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-76.99451</t>
+          <t>-76.99526</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>143</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>834930</t>
+          <t>305162</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SAN CARLOS DE LA CORPORACION</t>
+          <t>FE Y ALEGRIA 39</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12.05011</t>
+          <t>-12.0433</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-76.99931</t>
+          <t>-76.9899</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>846301</t>
+          <t>305261</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SAN MIGUEL EMPRENDEDOR</t>
+          <t>JOHANNES GUTENBERG</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-12.04564</t>
+          <t>-12.04798</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-76.99931</t>
+          <t>-76.99687</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>72</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>858756</t>
+          <t>305039</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>LA PRADERA II</t>
+          <t>GLORIOSOS HUSARES DE JUNIN</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-12.03034</t>
+          <t>-12.0515</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-76.96305</t>
+          <t>-76.9987</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1608</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>908252</t>
+          <t>304836</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>JUVENTUD CIENTIFICA</t>
+          <t>076 MICAELA BASTIDAS</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-12.043875</t>
+          <t>-12.05093</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-76.999552</t>
+          <t>-76.99544</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>147</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3725,37 +3725,37 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>999290</t>
+          <t>304841</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LA PIZARRA DE JUGUETE</t>
+          <t>081</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-12.03472</t>
+          <t>-12.03737</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-76.99981</t>
+          <t>-77.00589</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>207</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-EL_AGUSTINO.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-EL_AGUSTINO.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>304978</t>
+          <t>999290</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1046 JULIO RAMON RIBEYRO</t>
+          <t>LA PIZARRA DE JUGUETE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.05059</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.00892</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>-12.03472</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.99981</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>304704</t>
+          <t>908252</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>08 VILLA HERMOSA</t>
+          <t>JUVENTUD CIENTIFICA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.0408</t>
+          <t>183</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.98958</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>-12.043875</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.999552</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>304742</t>
+          <t>858756</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>013 SANTA ROSITA</t>
+          <t>LA PRADERA II</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.03934</t>
+          <t>362</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.99667</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>-12.03034</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.96305</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>304822</t>
+          <t>846301</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>069 NOCHETO LUIS ENRIQUE VI</t>
+          <t>SAN MIGUEL EMPRENDEDOR</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.04508</t>
+          <t>233</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.98547</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>-12.04564</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.99931</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>305100</t>
+          <t>834930</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HOGAR SAN MARTIN</t>
+          <t>SAN CARLOS DE LA CORPORACION</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.0542</t>
+          <t>305</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.0069</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>-12.05011</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.99931</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>305143</t>
+          <t>786806</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AUGUSTO N. WISSE</t>
+          <t>NICOLA DE BARI</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.03869</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.99016</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>-12.03104</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.99451</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>305044</t>
+          <t>714225</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1177 HEROES DEL CENEPA</t>
+          <t>CUNA JARDIN PARROQUIAL SAN JOSE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.05896</t>
+          <t>143</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.00256</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>-12.05879</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.99526</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>908252</t>
+          <t>602001</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JUVENTUD CIENTIFICA</t>
+          <t>ANTONIO ELEUTER</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.043875</t>
+          <t>240</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.999552</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>-12.05646</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.00601</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>304780</t>
+          <t>588340</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>048 SAN JUAN BOSCO</t>
+          <t>CRISTO REDENTOR</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.060027</t>
+          <t>421</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.002724</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>-12.05627</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.00747</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,37 +1059,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>304817</t>
+          <t>574036</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>068</t>
+          <t>DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.02776</t>
+          <t>104</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.99299</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>-12.0306</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.9987</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>305157</t>
+          <t>564259</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ALELUYA</t>
+          <t>SANTA RITA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.0504</t>
+          <t>803</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-76.99744</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>-12.03323</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.99779</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1183,42 +1183,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>305218</t>
+          <t>544068</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>DORA MAYER</t>
+          <t>VIRGEN MARIA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.05226</t>
+          <t>329</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.00583</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>-12.04911</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.00014</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>305299</t>
+          <t>490503</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ALEXANDER FLEMING</t>
+          <t>PASCUAL SACO OLIVEROS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.0321</t>
+          <t>851</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.9997</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>-12.03405</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.99737</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,42 +1307,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>588340</t>
+          <t>328248</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CRISTO REDENTOR</t>
+          <t>ESTRELLITA DE JESUS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.05627</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.00747</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>-12.04336</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.986953</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1369,42 +1369,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>834930</t>
+          <t>305360</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SAN CARLOS DE LA CORPORACION</t>
+          <t>NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.05011</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.99931</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>-12.0306</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.99846</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>305077</t>
+          <t>305299</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1187 SAN CAYETANO</t>
+          <t>ALEXANDER FLEMING</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.05678</t>
+          <t>240</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.00766</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>-12.0321</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.9997</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>305256</t>
+          <t>305261</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>IGNACIO MERINO</t>
+          <t>JOHANNES GUTENBERG</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.05523</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.00642</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>-12.04798</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.99687</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>602001</t>
+          <t>305256</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ANTONIO ELEUTER</t>
+          <t>IGNACIO MERINO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.05646</t>
+          <t>251</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.00601</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>-12.05523</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.00642</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,37 +1617,37 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>304879</t>
+          <t>305218</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0093 FERNANDO BELAUNDE TERRY</t>
+          <t>DORA MAYER</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.03924</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.99658</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>-12.05226</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.00583</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>858756</t>
+          <t>305162</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>LA PRADERA II</t>
+          <t>FE Y ALEGRIA 39</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.03034</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.96305</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>-12.0433</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.9899</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>305124</t>
+          <t>305157</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>NICOLAS DE PIEROLA</t>
+          <t>ALELUYA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.05079</t>
+          <t>178</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.0107</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>-12.0504</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-76.99744</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1803,37 +1803,37 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>786806</t>
+          <t>305143</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>NICOLA DE BARI</t>
+          <t>AUGUSTO N. WISSE</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.03104</t>
+          <t>206</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.99451</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-12.03869</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-76.99016</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>305119</t>
+          <t>305124</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>LA PRADERA II</t>
+          <t>NICOLAS DE PIEROLA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.0303</t>
+          <t>396</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-76.96305</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>-12.05079</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.0107</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>305063</t>
+          <t>305119</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1186 SANTA ROSA DE LIMA MILAGROSA</t>
+          <t>LA PRADERA II</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.0596</t>
+          <t>573</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.99679</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>-12.0303</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-76.96305</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>304756</t>
+          <t>305100</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>017 CUNA JARDIN</t>
+          <t>HOGAR SAN MARTIN</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.0514</t>
+          <t>217</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.99939</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>-12.0542</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.0069</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>305001</t>
+          <t>305077</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1169 ALMIRANTE MIGUEL GRAU S / 1169 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
+          <t>1187 SAN CAYETANO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.05152</t>
+          <t>364</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.00442</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>-12.05678</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.00766</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>304964</t>
+          <t>305063</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1045 NUESTRA SEÑORA DE FATIMA</t>
+          <t>1186 SANTA ROSA DE LIMA MILAGROSA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.0422</t>
+          <t>442</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.9894</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>-12.0596</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.99679</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>846301</t>
+          <t>305044</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SAN MIGUEL EMPRENDEDOR</t>
+          <t>1177 HEROES DEL CENEPA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.04564</t>
+          <t>315</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.99931</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>-12.05896</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-77.00256</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>544068</t>
+          <t>305039</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>VIRGEN MARIA</t>
+          <t>GLORIOSOS HUSARES DE JUNIN</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.04911</t>
+          <t>1608</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.00014</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>-12.0515</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-76.9987</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>490503</t>
+          <t>305020</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PASCUAL SACO OLIVEROS</t>
+          <t>1171 JORGE BASADRE GROHMANN</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.03405</t>
+          <t>802</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.99737</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>-12.055789</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-77.001602</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>564259</t>
+          <t>305001</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SANTA RITA</t>
+          <t>1169 ALMIRANTE MIGUEL GRAU S / 1169 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.03323</t>
+          <t>473</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.99779</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>-12.05152</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-77.00442</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2423,37 +2423,37 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>305360</t>
+          <t>304983</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL CARMEN</t>
+          <t>1047 JUANA INFANTES VERA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.0306</t>
+          <t>845</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-76.99846</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-12.03318</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-76.98888</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>304799</t>
+          <t>304978</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0049 ANTONIA MORENO DE CACERES</t>
+          <t>1046 JULIO RAMON RIBEYRO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.0521</t>
+          <t>205</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-77.0019</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>-12.05059</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-77.00892</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>304718</t>
+          <t>304964</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0009 JOSE MARIA ARGUEDAS</t>
+          <t>1045 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.02803</t>
+          <t>541</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-76.98938</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>-12.0422</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-76.9894</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>304921</t>
+          <t>304959</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>127 SAN JOSE</t>
+          <t>1044 MARIA REICHE NEWMANN</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.03325</t>
+          <t>887</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-77.00305</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>-12.044016</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-77.003</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>304935</t>
+          <t>304940</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>134 RAMIRO PRIALE</t>
+          <t>1025 MARIA PARADO DE BELLIDO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.031899</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-77.008878</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>-12.050187</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-77.006187</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>304959</t>
+          <t>304935</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1044 MARIA REICHE NEWMANN</t>
+          <t>134 RAMIRO PRIALE</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.044016</t>
+          <t>697</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-77.003</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>-12.031899</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-77.008878</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>305020</t>
+          <t>304921</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1171 JORGE BASADRE GROHMANN</t>
+          <t>127 SAN JOSE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.055789</t>
+          <t>782</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-77.001602</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>-12.03325</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-77.00305</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>304860</t>
+          <t>304916</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0085 JOSE DE LA TORRE UGARTE</t>
+          <t>115 TORIBIO RODRIGUEZ DE MENDOZA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.0379</t>
+          <t>854</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-76.99063</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>-12.0343</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-77.006</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>304983</t>
+          <t>304898</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1047 JUANA INFANTES VERA</t>
+          <t>112 HEROES DE LA BREÑA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.03318</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-76.98888</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>-12.03062</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-76.99718</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>304916</t>
+          <t>304879</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>115 TORIBIO RODRIGUEZ DE MENDOZA</t>
+          <t>0093 FERNANDO BELAUNDE TERRY</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.0343</t>
+          <t>441</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-77.006</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>-12.03924</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-76.99658</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>304761</t>
+          <t>304860</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>046 LOS LIBERTADORES DE AYACUCHO</t>
+          <t>0085 JOSE DE LA TORRE UGARTE</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.05624</t>
+          <t>839</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-76.99453</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>-12.0379</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-76.99063</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>304940</t>
+          <t>304841</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1025 MARIA PARADO DE BELLIDO</t>
+          <t>081</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.050187</t>
+          <t>207</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-77.006187</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>-12.03737</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-77.00589</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,42 +3167,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>574036</t>
+          <t>304836</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>DIVINO NIÑO JESUS</t>
+          <t>076 MICAELA BASTIDAS</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-12.0306</t>
+          <t>147</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-76.9987</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-12.05093</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-76.99544</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3229,37 +3229,37 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>999290</t>
+          <t>304822</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>LA PIZARRA DE JUGUETE</t>
+          <t>069 NOCHETO LUIS ENRIQUE VI</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.03472</t>
+          <t>207</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-76.99981</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>-12.04508</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-76.98547</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>304898</t>
+          <t>304817</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>112 HEROES DE LA BREÑA</t>
+          <t>068</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-12.03062</t>
+          <t>272</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-76.99718</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>-12.02776</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-76.99299</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,37 +3353,37 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>328248</t>
+          <t>304799</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ESTRELLITA DE JESUS</t>
+          <t>0049 ANTONIA MORENO DE CACERES</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-12.04336</t>
+          <t>709</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-76.986953</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-12.0521</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-77.0019</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>714225</t>
+          <t>304780</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CUNA JARDIN PARROQUIAL SAN JOSE</t>
+          <t>048 SAN JUAN BOSCO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.05879</t>
+          <t>270</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-76.99526</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>-12.060027</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-77.002724</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>305162</t>
+          <t>304761</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 39</t>
+          <t>046 LOS LIBERTADORES DE AYACUCHO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12.0433</t>
+          <t>877</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-76.9899</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>-12.05624</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>-76.99453</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>305261</t>
+          <t>304756</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>JOHANNES GUTENBERG</t>
+          <t>017 CUNA JARDIN</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-12.04798</t>
+          <t>565</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-76.99687</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>-12.0514</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-76.99939</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>305039</t>
+          <t>304742</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>GLORIOSOS HUSARES DE JUNIN</t>
+          <t>013 SANTA ROSITA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-12.0515</t>
+          <t>291</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-76.9987</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>-12.03934</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>-76.99667</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>304836</t>
+          <t>304718</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>076 MICAELA BASTIDAS</t>
+          <t>0009 JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-12.05093</t>
+          <t>727</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-76.99544</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>-12.02803</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-76.98938</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>304841</t>
+          <t>304704</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>081</t>
+          <t>08 VILLA HERMOSA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-12.03737</t>
+          <t>217</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-77.00589</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>-12.0408</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-76.98958</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-EL_AGUSTINO.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-EL_AGUSTINO.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
